--- a/diseases/d010/2015-2019.xlsx
+++ b/diseases/d010/2015-2019.xlsx
@@ -7940,7 +7940,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13408,7 +13408,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14738,7 +14738,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17398,7 +17398,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -18728,7 +18728,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20058,7 +20058,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -21388,7 +21388,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -25526,7 +25526,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26856,7 +26856,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -28186,7 +28186,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30846,7 +30846,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32176,7 +32176,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -33506,7 +33506,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -34836,7 +34836,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37496,7 +37496,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38826,7 +38826,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -40156,7 +40156,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -41486,7 +41486,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -42816,7 +42816,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -44146,7 +44146,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -45476,7 +45476,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -46806,7 +46806,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -48136,7 +48136,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -49466,7 +49466,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -50796,7 +50796,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -52126,7 +52126,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -53456,7 +53456,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -54786,7 +54786,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -56116,7 +56116,7 @@
       </c>
       <c r="AJ296" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK296" t="inlineStr">
@@ -57446,7 +57446,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -58776,7 +58776,7 @@
       </c>
       <c r="AJ310" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK310" t="inlineStr">
@@ -60106,7 +60106,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -61436,7 +61436,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -62766,7 +62766,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -64096,7 +64096,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -65426,7 +65426,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -66756,7 +66756,7 @@
       </c>
       <c r="AJ352" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK352" t="inlineStr">
@@ -68086,7 +68086,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -69416,7 +69416,7 @@
       </c>
       <c r="AJ366" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK366" t="inlineStr">
@@ -70746,7 +70746,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
